--- a/LISTAS_ORDENADAS/MA/Cerrojos Pasadores/BROCHE MEDIA SOMBRA.xlsx
+++ b/LISTAS_ORDENADAS/MA/Cerrojos Pasadores/BROCHE MEDIA SOMBRA.xlsx
@@ -737,14 +737,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="34" t="n">
-        <v>45154.58678499956</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="17">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -786,16 +782,6 @@
     <row r="12" ht="30" customHeight="1" s="17">
       <c r="A12" s="32" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23">
       <c r="C23" s="19" t="n"/>
     </row>
@@ -851,11 +837,9 @@
       </c>
       <c r="C29" s="38" t="n"/>
       <c r="D29" s="40" t="n">
-        <v>18.6</v>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31"/>
+        <v>20.6</v>
+      </c>
+    </row>
     <row r="32" ht="15" customHeight="1" s="17">
       <c r="A32" s="26" t="inlineStr">
         <is>
@@ -863,8 +847,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="17">
       <c r="A35" s="36" t="n"/>
       <c r="B35" s="36" t="n"/>
@@ -884,16 +866,12 @@
     <row r="39" ht="19.5" customHeight="1" s="17">
       <c r="B39" s="33" t="n"/>
     </row>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="17">
       <c r="A42" s="7" t="n"/>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="5" t="n"/>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="6" t="n"/>
     </row>
